--- a/allianz-rates-audit.xlsx
+++ b/allianz-rates-audit.xlsx
@@ -20,18 +20,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="บำนาญ 85A55" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider HB" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider HBP" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CI48" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CI48B" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CIMC" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CB Cancer" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CBN Cancer" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider TRN" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider TRC" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLA85 A85X" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MDP ดับเบิล พลัส" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ส่วนลดทุน" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ค่าปรับอาชีพ" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="หมายเหตุผู้ตรวจ" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider HS_S เอชเอส" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CI48" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CI48B" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CIMC" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CB Cancer" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider CBN Cancer" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider TRN" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rider TRC" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLA85 A85X" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MDP ดับเบิล พลัส" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ส่วนลดทุน" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ค่าปรับอาชีพ" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="หมายเหตุผู้ตรวจ" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -579,7 +580,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ดึงจากตารางเบี้ยจริง • ข้อมูล ณ เม.ย. 2026 • รวม 37 ผลิตภัณฑ์ (20 มีข้อมูล, 17 ยังไม่นำเข้า)</t>
+          <t>ดึงจากตารางเบี้ยจริง • ข้อมูล ณ เม.ย. 2026 • รวม 37 ผลิตภัณฑ์ (21 มีข้อมูล, 16 ยังไม่นำเข้า)</t>
         </is>
       </c>
     </row>
@@ -828,22 +829,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>MAFA9005</t>
+          <t>HS_S</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>มาย บำนาญ ไฟว์ A90/5 บำนาญแบบลดหย่อนได้ (มีเงินปันผล)</t>
+          <t>เอชเอส</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>สัญญาหลัก</t>
+          <t>สัญญาเพิ่มเติม</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>annuity</t>
+          <t>IPD</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -852,18 +853,18 @@
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>MAPA85A55</t>
+          <t>MAFA9005</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>มาย บำนาญ พลัส (บำนาญแบบลดหย่อนได้)</t>
+          <t>มาย บำนาญ ไฟว์ A90/5 บำนาญแบบลดหย่อนได้ (มีเงินปันผล)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -882,18 +883,18 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>MDP</t>
+          <t>MAPA85A55</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>มาย ดับเบิล พลัส (มีเงินปันผล)</t>
+          <t>มาย บำนาญ พลัส (บำนาญแบบลดหย่อนได้)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -903,7 +904,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>annuity</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -912,18 +913,18 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>377</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>MQR1206</t>
+          <t>MDP</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>มาย ควิก รีเทิร์น 12/6 (มีเงินปันผล)</t>
+          <t>มาย ดับเบิล พลัส (มีเงินปันผล)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -942,18 +943,18 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>MSI1808</t>
+          <t>MQR1206</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>มาย สมาร์ต อินเด็กซ์ 18/8 (แบบมีผลตอบแทนตามดัชนีอ้างอิง)</t>
+          <t>มาย ควิก รีเทิร์น 12/6 (มีเงินปันผล)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -978,12 +979,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>MWLA9021</t>
+          <t>MSI1808</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>มาย โฮล ไลฟ์ A90/21</t>
+          <t>มาย สมาร์ต อินเด็กซ์ 18/8 (แบบมีผลตอบแทนตามดัชนีอ้างอิง)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1002,18 +1003,18 @@
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>MWLA9906</t>
+          <t>MWLA9021</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>มาย เวลท์ เลกาซี A99/6 (มีเงินปันผล)</t>
+          <t>มาย โฮล ไลฟ์ A90/21</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1032,18 +1033,18 @@
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>MWLA9920</t>
+          <t>MWLA9906</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>มาย โฮล ไลฟ์ A99/20 (มีเงินปันผล)</t>
+          <t>มาย เวลท์ เลกาซี A99/6 (มีเงินปันผล)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1068,12 +1069,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SLA85</t>
+          <t>MWLA9920</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>อยุธยาชีวิตมั่นคง A85/X</t>
+          <t>มาย โฮล ไลฟ์ A99/20 (มีเงินปันผล)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1092,18 +1093,18 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>518</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T1010</t>
+          <t>SLA85</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>อยุธยาเฉพาะกาล 10/10</t>
+          <t>อยุธยาชีวิตมั่นคง A85/X</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1113,7 +1114,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>term</t>
+          <t>life</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1122,18 +1123,18 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>80</v>
+        <v>518</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>TM1</t>
+          <t>T1010</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>อยุธยาชั่วระยะเวลา</t>
+          <t>อยุธยาเฉพาะกาล 10/10</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1152,28 +1153,28 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>TM1</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>แบบเฉพาะกาล แปลงเป็นกรมธรรม์ได้</t>
+          <t>อยุธยาชั่วระยะเวลา</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>สัญญาเพิ่มเติม</t>
+          <t>สัญญาหลัก</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>TERM</t>
+          <t>term</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1182,18 +1183,18 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>TRN</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>แบบเฉพาะกาล</t>
+          <t>แบบเฉพาะกาล แปลงเป็นกรมธรรม์ได้</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1212,18 +1213,18 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>80</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>DVMFCPN_ALL</t>
+          <t>TRN</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ทันตกรรม เฟิร์สคลาส อัลตร้า แพลทินัม</t>
+          <t>แบบเฉพาะกาล</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1233,27 +1234,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>DENTAL</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>⏳ ยังไม่มีข้อมูล</t>
+          <t>TERM</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>✓ พร้อม audit</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>DVMFCPN_BDMS</t>
+          <t>DVMFCPN_ALL</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>ทันตกรรม เฟิร์สคลาส อัลตร้า แพลทินัม (รพ.กำหนด)</t>
+          <t>ทันตกรรม เฟิร์สคลาส อัลตร้า แพลทินัม</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1278,12 +1279,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>HBCI</t>
+          <t>DVMFCPN_BDMS</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>ค่ารักษาพยาบาลรายวัน + 5 โรคร้ายแรง</t>
+          <t>ทันตกรรม เฟิร์สคลาส อัลตร้า แพลทินัม (รพ.กำหนด)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1293,7 +1294,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>DAILY_HB_CI</t>
+          <t>DENTAL</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -1308,12 +1309,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>HSMFCBN_ALL</t>
+          <t>HBCI</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>เฟิร์สคลาส บียอนด์ แพลทินัม</t>
+          <t>ค่ารักษาพยาบาลรายวัน + 5 โรคร้ายแรง</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1323,7 +1324,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>IPD</t>
+          <t>DAILY_HB_CI</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -1338,12 +1339,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>HSMFCBN_BDMS</t>
+          <t>HSMFCBN_ALL</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>เฟิร์สคลาส บียอนด์ แพลทินัม (รพ.กำหนด)</t>
+          <t>เฟิร์สคลาส บียอนด์ แพลทินัม</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1368,12 +1369,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>HSMFCPN_ALL</t>
+          <t>HSMFCBN_BDMS</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>เฟิร์สคลาส อัลตร้า แพลทินัม</t>
+          <t>เฟิร์สคลาส บียอนด์ แพลทินัม (รพ.กำหนด)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1398,12 +1399,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>HSMFCPN_BDMS</t>
+          <t>HSMFCPN_ALL</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>เฟิร์สคลาส อัลตร้า แพลทินัม (รพ.กำหนด)</t>
+          <t>เฟิร์สคลาส อัลตร้า แพลทินัม</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1428,12 +1429,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>HSMHPDC</t>
+          <t>HSMFCPN_BDMS</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ปลดล็อค ดับเบิล แคร์</t>
+          <t>เฟิร์สคลาส อัลตร้า แพลทินัม (รพ.กำหนด)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1458,12 +1459,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>HSMHPSK</t>
+          <t>HSMHPDC</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ปลดล็อค สบายกระเป๋า</t>
+          <t>ปลดล็อค ดับเบิล แคร์</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1488,12 +1489,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>HS_S</t>
+          <t>HSMHPSK</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>เอชเอส</t>
+          <t>ปลดล็อค สบายกระเป๋า</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -5142,6 +5143,3924 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G132"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>คุ้มครองสุขภาพ เอชเอส (HS) (HS_S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>เบี้ย = เต็มราคาต่อปี (rate = full annual premium ต่อแผน) • ต่ออายุสูงสุด 89 ปี • มีตัวคูณอาชีพ (ดูชีท ค่าปรับอาชีพ) • 4 แผน · rate = เบี้ยเต็มต่อปีตามแผน · ต่ออายุถึง 89 (71+ เฉพาะต่ออายุ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>แผน</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>อายุต่ำสุด</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>อายุสูงสุด</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>เพศ</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>เบี้ยต่อปี (บาท)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>เฉพาะต่ออายุ?</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>เบี้ย/ปี (occ 1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>7885</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="11">
+        <f>E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>7885</v>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="15">
+        <f>E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>7278</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="11">
+        <f>E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>6065</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="15">
+        <f>E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>7278</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="11">
+        <f>E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>6065</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="15">
+        <f>E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>7278</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="11">
+        <f>E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>6065</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="15">
+        <f>E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>7278</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="11">
+        <f>E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>6065</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="15">
+        <f>E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>8734</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="11">
+        <f>E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>7278</v>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="15">
+        <f>E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>9462</v>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="11">
+        <f>E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>7885</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="15">
+        <f>E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>10918</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="11">
+        <f>E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>9098</v>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="15">
+        <f>E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>11646</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="11">
+        <f>E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>9705</v>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="15">
+        <f>E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>14557</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="11">
+        <f>E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>12131</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="15">
+        <f>E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>21835</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="11">
+        <f>E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>18196</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="15">
+        <f>E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>29114</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="11">
+        <f>E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>24262</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="15">
+        <f>E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>50949</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G29" s="11">
+        <f>E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>42458</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G30" s="15">
+        <f>E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>72785</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G31" s="11">
+        <f>E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>60654</v>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G32" s="15">
+        <f>E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>94621</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G33" s="11">
+        <f>E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>78850</v>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G34" s="15">
+        <f>E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>113545</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G35" s="11">
+        <f>E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>94620</v>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G36" s="15">
+        <f>E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>10382</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="11">
+        <f>E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>10382</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="15">
+        <f>E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>9583</v>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="11">
+        <f>E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="15">
+        <f>E40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>9583</v>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="11">
+        <f>E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="15">
+        <f>E42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>9583</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="11">
+        <f>E43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="15">
+        <f>E44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>9583</v>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="11">
+        <f>E45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="15">
+        <f>E46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="11">
+        <f>E47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>9583</v>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="15">
+        <f>E48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>12458</v>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="11">
+        <f>E49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>10382</v>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="15">
+        <f>E50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>14375</v>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="11">
+        <f>E51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>11979</v>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="15">
+        <f>E52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>15333</v>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="11">
+        <f>E53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>12778</v>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="15">
+        <f>E54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>19166</v>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="11">
+        <f>E55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="C56" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>15972</v>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="15">
+        <f>E56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>28750</v>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="11">
+        <f>E57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C58" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>23958</v>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="15">
+        <f>E58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>38333</v>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="11">
+        <f>E59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>31944</v>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="15">
+        <f>E60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>67082</v>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G61" s="11">
+        <f>E61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="C62" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>55902</v>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G62" s="15">
+        <f>E62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>95832</v>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G63" s="11">
+        <f>E63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="C64" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>79860</v>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G64" s="15">
+        <f>E64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>124582</v>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G65" s="11">
+        <f>E65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="C66" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>103818</v>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G66" s="15">
+        <f>E66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>149498</v>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G67" s="11">
+        <f>E67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="C68" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>124582</v>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G68" s="15">
+        <f>E68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>13892</v>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="11">
+        <f>E69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C70" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>13892</v>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="15">
+        <f>E70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>12823</v>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="11">
+        <f>E71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C72" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>10686</v>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="15">
+        <f>E72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>12823</v>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="11">
+        <f>E73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C74" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>10686</v>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="15">
+        <f>E74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>12823</v>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="11">
+        <f>E75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C76" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>10686</v>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="15">
+        <f>E76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>12823</v>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="11">
+        <f>E77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C78" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>10686</v>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="15">
+        <f>E78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>15388</v>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="11">
+        <f>E79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C80" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>12823</v>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="15">
+        <f>E80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>16670</v>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="11">
+        <f>E81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="C82" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>13892</v>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="15">
+        <f>E82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>19235</v>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="11">
+        <f>E83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>16029</v>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="15">
+        <f>E84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>20517</v>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="11">
+        <f>E85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="C86" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>17098</v>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="15">
+        <f>E86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>25646</v>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="11">
+        <f>E87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="C88" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>21372</v>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="15">
+        <f>E88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>38470</v>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="11">
+        <f>E89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C90" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>32058</v>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="15">
+        <f>E90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>51293</v>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="11">
+        <f>E91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="C92" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>42744</v>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="15">
+        <f>E92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>89762</v>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G93" s="11">
+        <f>E93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>74802</v>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G94" s="15">
+        <f>E94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>128232</v>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G95" s="11">
+        <f>E95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>106860</v>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G96" s="15">
+        <f>E96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>166702</v>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G97" s="11">
+        <f>E97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>138918</v>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G98" s="15">
+        <f>E98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>200042</v>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G99" s="11">
+        <f>E99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>166702</v>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G100" s="15">
+        <f>E100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>17687</v>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="11">
+        <f>E101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>17687</v>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="15">
+        <f>E102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>16326</v>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="11">
+        <f>E103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>13605</v>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="15">
+        <f>E104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>16326</v>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="11">
+        <f>E105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>13605</v>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="15">
+        <f>E106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>16326</v>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="11">
+        <f>E107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>13605</v>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" s="15">
+        <f>E108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>16326</v>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="11">
+        <f>E109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>13605</v>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="15">
+        <f>E110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C111" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>19591</v>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="11">
+        <f>E111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>16326</v>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G112" s="15">
+        <f>E112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C113" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>21224</v>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="11">
+        <f>E113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>17687</v>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G114" s="15">
+        <f>E114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C115" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>24489</v>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" s="11">
+        <f>E115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="C116" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>20408</v>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" s="15">
+        <f>E116</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C117" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>26122</v>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G117" s="11">
+        <f>E117</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="C118" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>21768</v>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="15">
+        <f>E118</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>32652</v>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="11">
+        <f>E119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="C120" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>27210</v>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" s="15">
+        <f>E120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C121" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>48978</v>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="11">
+        <f>E121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C122" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>40815</v>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="15">
+        <f>E122</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C123" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>65304</v>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G123" s="11">
+        <f>E123</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="C124" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>54420</v>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G124" s="15">
+        <f>E124</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C125" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>114282</v>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G125" s="11">
+        <f>E125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="C126" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>95235</v>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G126" s="15">
+        <f>E126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C127" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>163260</v>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G127" s="11">
+        <f>E127</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="C128" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>136050</v>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G128" s="15">
+        <f>E128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C129" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>212238</v>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G129" s="11">
+        <f>E129</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="C130" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>176865</v>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G130" s="15">
+        <f>E130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C131" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>254686</v>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G131" s="11">
+        <f>E131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="C132" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>212238</v>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="G132" s="15">
+        <f>E132</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8214,7 +12133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13392,7 +17311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14670,7 +18589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17748,7 +21667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30234,2484 +34153,6 @@
       </c>
       <c r="G418" s="15">
         <f>E418*1000.0</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>แบบเฉพาะกาล 5/5 (TRN) (TRN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>rate_per = 1000 บาททุน • ต่ออายุสูงสุด 59 ปี • Term life rider, อายุรับ 20–59</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>แผน</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>อายุต่ำสุด</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>อายุสูงสุด</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>เพศ</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>อัตราเบี้ย (บาท/1,000 ทุน)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>เฉพาะต่ออายุ?</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>เบี้ยตัวอย่าง ทุน 1M</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="11">
-        <f>E5*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="15">
-        <f>E6*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="11">
-        <f>E7*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="15">
-        <f>E8*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="11">
-        <f>E9*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="15">
-        <f>E10*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="11">
-        <f>E11*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="15">
-        <f>E12*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="11">
-        <f>E13*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="15">
-        <f>E14*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="11">
-        <f>E15*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="15">
-        <f>E16*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="11">
-        <f>E17*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="15">
-        <f>E18*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="11">
-        <f>E19*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="15">
-        <f>E20*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="11">
-        <f>E21*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="15">
-        <f>E22*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="11">
-        <f>E23*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="C24" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="15">
-        <f>E24*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="11">
-        <f>E25*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C26" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="15">
-        <f>E26*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="11">
-        <f>E27*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="15">
-        <f>E28*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="11">
-        <f>E29*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="C30" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="15">
-        <f>E30*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="11">
-        <f>E31*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="C32" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="15">
-        <f>E32*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="11">
-        <f>E33*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="15">
-        <f>E34*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="11">
-        <f>E35*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="C36" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="15">
-        <f>E36*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="C37" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="11">
-        <f>E37*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="15">
-        <f>E38*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="C39" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="11">
-        <f>E39*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="15">
-        <f>E40*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="11">
-        <f>E41*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="C42" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="15">
-        <f>E42*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="11">
-        <f>E43*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="C44" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="15">
-        <f>E44*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="11">
-        <f>E45*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="C46" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="15">
-        <f>E46*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="11">
-        <f>E47*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="C48" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="15">
-        <f>E48*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="C49" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="11">
-        <f>E49*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="C50" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="15">
-        <f>E50*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="C51" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="11">
-        <f>E51*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="C52" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E52" s="14" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="15">
-        <f>E52*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="C53" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="11">
-        <f>E53*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="C54" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="15">
-        <f>E54*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="C55" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="11">
-        <f>E55*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B56" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="C56" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="15">
-        <f>E56*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="C57" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="11">
-        <f>E57*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="C58" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="15">
-        <f>E58*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="C59" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="11">
-        <f>E59*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B60" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="C60" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="15">
-        <f>E60*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="C61" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="11">
-        <f>E61*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B62" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="C62" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="15">
-        <f>E62*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="C63" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="11">
-        <f>E63*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B64" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="C64" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="15">
-        <f>E64*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="C65" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="11">
-        <f>E65*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="C66" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="15">
-        <f>E66*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="n">
-        <v>51</v>
-      </c>
-      <c r="C67" s="9" t="n">
-        <v>51</v>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="11">
-        <f>E67*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B68" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="C68" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="15">
-        <f>E68*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="C69" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="11">
-        <f>E69*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="C70" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="15">
-        <f>E70*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="C71" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="11">
-        <f>E71*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B72" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="C72" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="15">
-        <f>E72*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="C73" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="11">
-        <f>E73*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="C74" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="D74" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E74" s="14" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="15">
-        <f>E74*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="C75" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="11">
-        <f>E75*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="C76" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="D76" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="n">
-        <v>15.37</v>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="15">
-        <f>E76*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="C77" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>9.24</v>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="11">
-        <f>E77*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="C78" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="n">
-        <v>16.54</v>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="15">
-        <f>E78*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="C79" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="11">
-        <f>E79*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B80" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="C80" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="15">
-        <f>E80*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="C81" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="11">
-        <f>E81*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="15">
-        <f>E82*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="C83" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>หญิง</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="11">
-        <f>E83*1000.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="C84" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>ชาย</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v>21.02</v>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G84" s="15">
-        <f>E84*1000.0</f>
         <v/>
       </c>
     </row>
@@ -34263,11 +35704,11 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>unisex</t>
+          <t>gender_specific</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -34277,7 +35718,7 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ใช่</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -34287,7 +35728,7 @@
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>11 year</t>
         </is>
       </c>
       <c r="K31" s="9" t="n">
@@ -34780,6 +36221,2484 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>แบบเฉพาะกาล 5/5 (TRN) (TRN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>rate_per = 1000 บาททุน • ต่ออายุสูงสุด 59 ปี • Term life rider, อายุรับ 20–59</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>แผน</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>อายุต่ำสุด</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>อายุสูงสุด</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>เพศ</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>อัตราเบี้ย (บาท/1,000 ทุน)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>เฉพาะต่ออายุ?</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>เบี้ยตัวอย่าง ทุน 1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="11">
+        <f>E5*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="15">
+        <f>E6*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="11">
+        <f>E7*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="15">
+        <f>E8*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="11">
+        <f>E9*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="15">
+        <f>E10*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="11">
+        <f>E11*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="15">
+        <f>E12*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="11">
+        <f>E13*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="15">
+        <f>E14*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="11">
+        <f>E15*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="15">
+        <f>E16*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="11">
+        <f>E17*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="15">
+        <f>E18*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="11">
+        <f>E19*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="15">
+        <f>E20*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="11">
+        <f>E21*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="15">
+        <f>E22*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="11">
+        <f>E23*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="15">
+        <f>E24*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="11">
+        <f>E25*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="15">
+        <f>E26*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="11">
+        <f>E27*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="15">
+        <f>E28*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="11">
+        <f>E29*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="15">
+        <f>E30*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="11">
+        <f>E31*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="15">
+        <f>E32*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="11">
+        <f>E33*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="15">
+        <f>E34*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="11">
+        <f>E35*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="15">
+        <f>E36*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="11">
+        <f>E37*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="15">
+        <f>E38*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="11">
+        <f>E39*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="15">
+        <f>E40*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="11">
+        <f>E41*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="15">
+        <f>E42*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="11">
+        <f>E43*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="15">
+        <f>E44*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="11">
+        <f>E45*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="15">
+        <f>E46*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="11">
+        <f>E47*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="15">
+        <f>E48*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="11">
+        <f>E49*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="15">
+        <f>E50*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="11">
+        <f>E51*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="15">
+        <f>E52*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="11">
+        <f>E53*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="15">
+        <f>E54*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="11">
+        <f>E55*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="C56" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="15">
+        <f>E56*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="11">
+        <f>E57*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="C58" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="15">
+        <f>E58*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="11">
+        <f>E59*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="15">
+        <f>E60*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="11">
+        <f>E61*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="C62" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="15">
+        <f>E62*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="11">
+        <f>E63*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="C64" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="15">
+        <f>E64*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="11">
+        <f>E65*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="C66" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="15">
+        <f>E66*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="11">
+        <f>E67*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="C68" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="15">
+        <f>E68*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="11">
+        <f>E69*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="C70" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="15">
+        <f>E70*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="11">
+        <f>E71*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="C72" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="15">
+        <f>E72*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="11">
+        <f>E73*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="C74" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="15">
+        <f>E74*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="11">
+        <f>E75*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="C76" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="15">
+        <f>E76*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="11">
+        <f>E77*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="C78" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="15">
+        <f>E78*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="11">
+        <f>E79*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="C80" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="15">
+        <f>E80*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="11">
+        <f>E81*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="C82" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="15">
+        <f>E82*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>หญิง</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="11">
+        <f>E83*1000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>ชาย</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="15">
+        <f>E84*1000.0</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42057,7 +45976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -57675,7 +61594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -69063,7 +72982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -69843,13 +73762,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -70185,12 +74104,12 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>CIMC</t>
+          <t>HS_S</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>โรคร้ายแรง มัลติ แคร์</t>
+          <t>เอชเอส</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
@@ -70203,12 +74122,12 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>CIMC</t>
+          <t>HS_S</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>โรคร้ายแรง มัลติ แคร์</t>
+          <t>เอชเอส</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
@@ -70221,12 +74140,12 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>CIMC</t>
+          <t>HS_S</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>โรคร้ายแรง มัลติ แคร์</t>
+          <t>เอชเอส</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -70239,18 +74158,90 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>CIMC</t>
+          <t>HS_S</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>โรคร้ายแรง มัลติ แคร์</t>
+          <t>เอชเอส</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D24" s="17" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>CIMC</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>โรคร้ายแรง มัลติ แคร์</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>CIMC</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>โรคร้ายแรง มัลติ แคร์</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>CIMC</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>โรคร้ายแรง มัลติ แคร์</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>CIMC</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>โรคร้ายแรง มัลติ แคร์</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="17" t="n">
         <v>1.45</v>
       </c>
     </row>
@@ -70263,7 +74254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -70437,7 +74428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -70965,6 +74956,146 @@
         <is>
           <t>—</t>
         </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>HS_S</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>เอชเอส</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>เอชเอส แผน 1</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>HS_S</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>เอชเอส</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>เอชเอส แผน 2</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>HS_S</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>เอชเอส</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>เอชเอส แผน 3</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>HS_S</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>เอชเอส</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>เอชเอส แผน 4</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
